--- a/database.xlsx
+++ b/database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kinop\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kinop\Documents\Billing-Planning-for-Trickcal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24010DF-E97F-4F7A-BBD4-D7A87A751EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEB7F55-DDE3-4C59-9A11-582EABD06086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="6" xr2:uid="{0E240044-467D-4804-AB3F-8E98DCC96A0D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{0E240044-467D-4804-AB3F-8E98DCC96A0D}"/>
   </bookViews>
   <sheets>
     <sheet name="特別構成商品" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="204">
   <si>
     <t>商品名</t>
     <rPh sb="0" eb="3">
@@ -125,98 +125,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>１周年ロビーパック</t>
-    <rPh sb="1" eb="3">
-      <t>シュウネン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>１周年特別募集パック</t>
-    <rPh sb="1" eb="5">
-      <t>シュウネントクベツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：キャンディ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：スタキャン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：信仰</t>
-    <rPh sb="5" eb="7">
-      <t>シンコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：啓示</t>
-    <rPh sb="5" eb="7">
-      <t>ケイジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：説教</t>
-    <rPh sb="5" eb="7">
-      <t>セッキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：教団</t>
-    <rPh sb="5" eb="7">
-      <t>キョウダン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：成長</t>
-    <rPh sb="5" eb="7">
-      <t>セイチョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：栄光</t>
-    <rPh sb="5" eb="7">
-      <t>エイコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：選別</t>
-    <rPh sb="5" eb="7">
-      <t>センベツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：使徒募集</t>
-    <rPh sb="5" eb="9">
-      <t>シトボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：性格募集</t>
-    <rPh sb="5" eb="9">
-      <t>セイカクボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：カード</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>無料エリーフ</t>
     <rPh sb="0" eb="2">
       <t>ムリョウ</t>
@@ -276,16 +184,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>所持伝説カードの選択箱</t>
-    <rPh sb="0" eb="4">
-      <t>ショジデンセツ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>センタクバコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>特急くれよん</t>
     <rPh sb="0" eb="2">
       <t>トッキュウ</t>
@@ -338,19 +236,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ロビーイラスト:祈りの果てに辿り着いた世界</t>
-    <rPh sb="8" eb="9">
-      <t>イノ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ハ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>タド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>エルダイン使徒合成カード</t>
     <rPh sb="5" eb="7">
       <t>シト</t>
@@ -652,19 +537,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>所持エルダイン使徒選択チケット</t>
-    <rPh sb="0" eb="2">
-      <t>ショジ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>シト</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>★3純粋の使徒ガチャチケット</t>
     <rPh sb="2" eb="4">
       <t>ジュンスイ</t>
@@ -685,23 +557,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>無料★3募集チケット</t>
-    <rPh sb="0" eb="3">
-      <t>ムリョウホシ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>★3募集チケット</t>
-    <rPh sb="2" eb="4">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>使徒パック</t>
     <rPh sb="0" eb="2">
       <t>シト</t>
@@ -744,10 +599,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ジョアン：くれよん</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>購入可能数</t>
     <rPh sb="0" eb="5">
       <t>コウニュウカノウスウ</t>
@@ -1407,194 +1258,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ジョアン：奇跡</t>
-    <rPh sb="5" eb="7">
-      <t>キセキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：敬虔</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：キャンディいっぱい</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：意思</t>
-    <rPh sb="5" eb="7">
-      <t>イシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ベリータ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：悔い改め</t>
-    <rPh sb="5" eb="6">
-      <t>ク</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>アラタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：感謝</t>
-    <rPh sb="5" eb="7">
-      <t>カンシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：確信</t>
-    <rPh sb="5" eb="7">
-      <t>カクシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：原則</t>
-    <rPh sb="5" eb="7">
-      <t>ゲンソク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エピカ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジョアン：恩籠</t>
-    <rPh sb="5" eb="7">
-      <t>オンカゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3500K</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ウサギトークン*10</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ベリータの使徒証*20</t>
-    <rPh sb="5" eb="8">
-      <t>シトアカシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>7000K</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>伝説のカードガチャチケット</t>
-    <rPh sb="0" eb="2">
-      <t>デンセツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エピカの使徒証*20</t>
-    <rPh sb="4" eb="7">
-      <t>シトアカシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>公演するエピカポスター</t>
-    <rPh sb="0" eb="2">
-      <t>コウエン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>良い日、幸せなエピカポスター</t>
-    <rPh sb="0" eb="1">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>シアワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>応援するクロエとディアナフィギュア</t>
-    <rPh sb="0" eb="2">
-      <t>オウエン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あなただけの更新エピカフィギュア</t>
-    <rPh sb="6" eb="8">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あなただけの今日のエピカポスター</t>
-    <rPh sb="6" eb="8">
-      <t>キョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あなただけのエピカフレーム</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>公演するエピカポスター*1</t>
-    <rPh sb="0" eb="2">
-      <t>コウエン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>良い日、幸せなエピカポスター*1</t>
-    <rPh sb="0" eb="1">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>シアワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>応援するクロエとディアナフィギュア*1</t>
-    <rPh sb="0" eb="2">
-      <t>オウエン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あなただけの更新エピカフィギュア*1</t>
-    <rPh sb="6" eb="8">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あなただけの今日のエピカポスター*1</t>
-    <rPh sb="6" eb="8">
-      <t>キョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あなただけのエピカフレーム*1</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1652,25 +1316,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プロフアイコン:信仰と親交の間アイコン フィギュア:司祭の外出フィギュア</t>
-    <rPh sb="8" eb="10">
-      <t>シンコウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シンコウ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ハザマ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>シサイ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ガイシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>探検パス(2026/10月)</t>
     <rPh sb="0" eb="2">
       <t>タンケン</t>
@@ -1710,6 +1355,321 @@
     <rPh sb="59" eb="62">
       <t>ザイリョウバコ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一緒にずっとロビーパック</t>
+    <rPh sb="0" eb="2">
+      <t>イッショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウサギトークン*3,ロビー背景 一緒にずっと(昼)*1</t>
+    <rPh sb="13" eb="15">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イッショ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヒル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１周年キャンディパック</t>
+    <rPh sb="1" eb="3">
+      <t>シュウネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1周年たっぷりパック</t>
+    <rPh sb="1" eb="3">
+      <t>シュウネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウサギトークン*2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘイリーの挨拶パック</t>
+    <rPh sb="5" eb="7">
+      <t>アイサツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘイリーの交渉パック</t>
+    <rPh sb="5" eb="7">
+      <t>コウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘイリーの満足パック</t>
+    <rPh sb="5" eb="7">
+      <t>マンゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘイリーの進級パック</t>
+    <rPh sb="5" eb="7">
+      <t>シンキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘイリーの装備パック</t>
+    <rPh sb="5" eb="7">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>星に願い事ヨミパック</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ネガ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ゴト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘイリーの指揮パック</t>
+    <rPh sb="5" eb="7">
+      <t>シキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘイリーのイキりパック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘイリーの意思パック</t>
+    <rPh sb="5" eb="7">
+      <t>イシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>★3所持一般使徒選択チケット</t>
+    <rPh sb="2" eb="4">
+      <t>ショジ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>イッパンシト</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヨミの使徒証*20</t>
+    <rPh sb="3" eb="5">
+      <t>シト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔法!疑いの眼差し</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ウタガ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>マナザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月光変身!ヨミポスター</t>
+    <rPh sb="0" eb="4">
+      <t>ゲッコウヘンシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔法少女と戦うヴィヴィフィギュア</t>
+    <rPh sb="0" eb="4">
+      <t>マホウショウジョ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タタカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔法少女と戦うヨミフィギュア</t>
+    <rPh sb="0" eb="4">
+      <t>マホウショウジョ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タタカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月にかかった魔法少女</t>
+    <rPh sb="0" eb="1">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>マホウショウジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔法少女ヨミフレーム</t>
+    <rPh sb="0" eb="4">
+      <t>マホウショウジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポスター:魔法!疑いの眼差し</t>
+    <rPh sb="5" eb="7">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ウタガ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>マナザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポスター月光変身!ヨミポスター</t>
+    <rPh sb="4" eb="8">
+      <t>ゲッコウヘンシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィギュア:魔法少女と戦うヴィヴィのフィギュア</t>
+    <rPh sb="6" eb="10">
+      <t>マホウショウジョ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>タタカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィギュア:魔法少女と戦うヨミのフィギュア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キーホルダー:月にかかった魔法少女</t>
+    <rPh sb="7" eb="8">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>マホウショウジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロフアイコン:信仰と信仰の間アイコン フィギュア:司祭の外出フィギュア</t>
+    <rPh sb="8" eb="10">
+      <t>シンコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シンコウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ハザマ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シサイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ガイシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミーの秘密パック</t>
+    <rPh sb="4" eb="6">
+      <t>ヒミツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミーの休息パック</t>
+    <rPh sb="4" eb="6">
+      <t>キュウソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミーの足跡パック</t>
+    <rPh sb="4" eb="6">
+      <t>アシアト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミーの計画パック</t>
+    <rPh sb="4" eb="6">
+      <t>ケイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミーの水遊びパック</t>
+    <rPh sb="4" eb="6">
+      <t>ミズアソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミーの目標パック</t>
+    <rPh sb="4" eb="6">
+      <t>モクヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミーの満足パック</t>
+    <rPh sb="4" eb="6">
+      <t>マンゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミーのスカウトパック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミーの回想パック</t>
+    <rPh sb="4" eb="6">
+      <t>カイソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1500K</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウサギトークン*5</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2094,70 +2054,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E721CC5-3751-4AD8-8501-A75691DE05E7}">
-  <dimension ref="A1:BC35"/>
+  <dimension ref="A1:BC29"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <sheetData>
     <row r="1" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="BC1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="S2" t="s">
         <v>3</v>
       </c>
       <c r="U2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="AZ2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="K3" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="U3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="W3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="AB3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="AE3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="AG3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AI3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="AM3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.7">
@@ -2165,52 +2125,52 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O4" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q4" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" t="s">
-        <v>84</v>
-      </c>
-      <c r="L4" t="s">
-        <v>113</v>
-      </c>
-      <c r="M4" t="s">
-        <v>114</v>
-      </c>
-      <c r="N4" t="s">
-        <v>115</v>
-      </c>
-      <c r="O4" t="s">
-        <v>85</v>
-      </c>
-      <c r="P4" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>40</v>
       </c>
       <c r="R4" t="s">
         <v>2</v>
@@ -2219,112 +2179,112 @@
         <v>3</v>
       </c>
       <c r="T4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="U4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="V4" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="W4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="X4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="Z4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="AA4" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="AB4" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="AC4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AO4" t="s">
         <v>51</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AP4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR4" t="s">
         <v>50</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AS4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AU4" t="s">
         <v>57</v>
       </c>
-      <c r="AF4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI4" t="s">
+      <c r="AV4" t="s">
         <v>58</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AW4" t="s">
         <v>59</v>
       </c>
-      <c r="AK4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>71</v>
-      </c>
-      <c r="AT4" t="s">
+      <c r="AX4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>61</v>
+      </c>
+      <c r="AZ4" t="s">
         <v>72</v>
       </c>
-      <c r="AU4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>91</v>
-      </c>
       <c r="BA4" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="BB4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.7">
@@ -2332,16 +2292,16 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="C5">
         <v>160</v>
       </c>
       <c r="R5" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="BC5" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.7">
@@ -2349,7 +2309,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="C6">
         <v>680</v>
@@ -2366,7 +2326,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="C7">
         <v>1600</v>
@@ -2378,7 +2338,7 @@
         <v>10</v>
       </c>
       <c r="R7" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="S7">
         <v>300</v>
@@ -2387,7 +2347,7 @@
         <v>300</v>
       </c>
       <c r="W7" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="X7">
         <v>1500</v>
@@ -2398,131 +2358,122 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C8">
         <v>680</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="BB8" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="BC8" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C9">
-        <v>3000</v>
-      </c>
-      <c r="F9">
-        <v>850</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <v>10</v>
-      </c>
-      <c r="BB9" t="s">
-        <v>39</v>
+        <v>160</v>
+      </c>
+      <c r="R9" t="s">
+        <v>11</v>
+      </c>
+      <c r="S9">
+        <v>1111</v>
       </c>
     </row>
     <row r="10" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C10">
-        <v>5200</v>
-      </c>
-      <c r="H10">
-        <v>30</v>
-      </c>
-      <c r="I10">
-        <v>30</v>
-      </c>
-      <c r="R10" t="s">
-        <v>40</v>
+        <v>1000</v>
+      </c>
+      <c r="F10">
+        <v>300</v>
+      </c>
+      <c r="G10">
+        <v>300</v>
       </c>
       <c r="S10">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="T10">
-        <v>500</v>
+        <v>300</v>
+      </c>
+      <c r="X10">
+        <v>2000</v>
+      </c>
+      <c r="AF10">
+        <v>2</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="B11" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="C11">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="F11">
-        <v>80</v>
-      </c>
-      <c r="S11">
-        <v>200</v>
-      </c>
-      <c r="X11">
-        <v>500</v>
-      </c>
-      <c r="AK11">
-        <v>5</v>
-      </c>
-      <c r="AZ11">
+        <v>850</v>
+      </c>
+      <c r="H11">
         <v>10</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>170</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C12">
+        <v>1000</v>
+      </c>
+      <c r="F12">
         <v>300</v>
       </c>
-      <c r="F12">
-        <v>80</v>
-      </c>
-      <c r="T12">
-        <v>100</v>
-      </c>
-      <c r="AI12">
+      <c r="G12">
+        <v>300</v>
+      </c>
+      <c r="H12">
         <v>10</v>
       </c>
-      <c r="AK12">
-        <v>5</v>
-      </c>
-      <c r="AZ12">
-        <v>10</v>
+      <c r="BB12" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C13">
         <v>1000</v>
@@ -2530,19 +2481,22 @@
       <c r="F13">
         <v>300</v>
       </c>
-      <c r="H13">
+      <c r="G13">
+        <v>300</v>
+      </c>
+      <c r="I13">
         <v>10</v>
       </c>
-      <c r="AZ13">
-        <v>20</v>
+      <c r="BB13" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C14">
         <v>1000</v>
@@ -2550,433 +2504,326 @@
       <c r="F14">
         <v>300</v>
       </c>
-      <c r="I14">
+      <c r="G14">
+        <v>300</v>
+      </c>
+      <c r="J14">
         <v>10</v>
       </c>
-      <c r="AZ14">
-        <v>20</v>
+      <c r="BB14" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C15">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F15">
-        <v>300</v>
-      </c>
-      <c r="J15">
+        <v>850</v>
+      </c>
+      <c r="AE15">
         <v>10</v>
       </c>
-      <c r="AZ15">
-        <v>20</v>
+      <c r="AF15">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="C16">
-        <v>1000</v>
+        <v>5200</v>
       </c>
       <c r="F16">
-        <v>300</v>
-      </c>
-      <c r="AM16">
-        <v>10</v>
-      </c>
-      <c r="AO16">
-        <v>60</v>
-      </c>
-      <c r="AR16">
-        <v>30</v>
-      </c>
-      <c r="AS16">
-        <v>20</v>
+        <v>1500</v>
+      </c>
+      <c r="G16">
+        <v>1500</v>
+      </c>
+      <c r="W16" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="C17">
-        <v>3000</v>
-      </c>
-      <c r="F17">
-        <v>850</v>
-      </c>
-      <c r="AF17">
-        <v>4</v>
+        <v>10000</v>
       </c>
       <c r="BA17" t="s">
-        <v>81</v>
+        <v>158</v>
+      </c>
+      <c r="BB17" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>176</v>
       </c>
       <c r="B18" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="C18">
-        <v>5200</v>
-      </c>
-      <c r="F18">
-        <v>1500</v>
-      </c>
-      <c r="G18">
-        <v>1500</v>
-      </c>
-      <c r="W18" t="s">
-        <v>82</v>
+        <v>12800</v>
+      </c>
+      <c r="H18">
+        <v>150</v>
+      </c>
+      <c r="R18" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C19">
-        <v>10000</v>
-      </c>
-      <c r="F19">
-        <v>4580</v>
-      </c>
-      <c r="G19">
-        <f>4580*2</f>
-        <v>9160</v>
+        <v>12800</v>
+      </c>
+      <c r="I19">
+        <v>150</v>
+      </c>
+      <c r="K19">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>178</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="C20">
-        <v>10000</v>
+        <v>12800</v>
+      </c>
+      <c r="J20">
+        <v>150</v>
       </c>
       <c r="R20" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH20">
-        <v>30</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="B21" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C21">
-        <v>12800</v>
-      </c>
-      <c r="H21">
-        <v>150</v>
-      </c>
-      <c r="K21">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="F21">
+        <v>80</v>
+      </c>
+      <c r="S21">
+        <v>100</v>
+      </c>
+      <c r="T21">
+        <v>100</v>
+      </c>
+      <c r="AI21">
+        <v>10</v>
+      </c>
+      <c r="AZ21">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="B22" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C22">
-        <v>12800</v>
-      </c>
-      <c r="I22">
+        <v>1000</v>
+      </c>
+      <c r="F22">
+        <v>300</v>
+      </c>
+      <c r="AQ22">
+        <v>90</v>
+      </c>
+      <c r="AT22">
+        <v>30</v>
+      </c>
+      <c r="AV22">
         <v>150</v>
       </c>
-      <c r="O22">
-        <v>3</v>
+      <c r="AX22">
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>195</v>
       </c>
       <c r="B23" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C23">
-        <v>12800</v>
-      </c>
-      <c r="J23">
+        <v>1000</v>
+      </c>
+      <c r="F23">
+        <v>300</v>
+      </c>
+      <c r="G23">
+        <v>300</v>
+      </c>
+      <c r="AF23">
+        <v>1</v>
+      </c>
+      <c r="BB23" t="s">
         <v>150</v>
-      </c>
-      <c r="R23" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>196</v>
       </c>
       <c r="B24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="R24" t="s">
-        <v>87</v>
+        <v>125</v>
+      </c>
+      <c r="C24">
+        <v>2400</v>
+      </c>
+      <c r="F24">
+        <v>600</v>
+      </c>
+      <c r="H24">
+        <v>10</v>
+      </c>
+      <c r="I24">
+        <v>10</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="BA24" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A25" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="B25" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C25">
-        <v>300</v>
+        <v>2400</v>
       </c>
       <c r="F25">
-        <v>80</v>
-      </c>
-      <c r="H25">
-        <v>3</v>
+        <v>600</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>600</v>
+      </c>
+      <c r="T25">
+        <v>600</v>
+      </c>
+      <c r="AZ25">
+        <v>40</v>
+      </c>
+      <c r="BB25" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A26" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="B26" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="C26">
-        <v>300</v>
+        <v>5200</v>
       </c>
       <c r="F26">
-        <v>80</v>
-      </c>
-      <c r="I26">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="S26">
+        <v>500</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>500</v>
+      </c>
+      <c r="AG26">
+        <v>400</v>
+      </c>
+      <c r="BB26" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A27" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="B27" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C27">
-        <v>1000</v>
-      </c>
-      <c r="F27">
-        <v>300</v>
-      </c>
-      <c r="S27">
-        <v>300</v>
-      </c>
-      <c r="T27">
-        <v>300</v>
-      </c>
-      <c r="AZ27">
-        <v>20</v>
-      </c>
-      <c r="BB27" t="s">
-        <v>170</v>
+        <v>10000</v>
+      </c>
+      <c r="G27">
+        <v>100</v>
+      </c>
+      <c r="L27">
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A28" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B28" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C28">
-        <v>3000</v>
-      </c>
-      <c r="F28">
-        <v>850</v>
-      </c>
-      <c r="G28">
-        <v>850</v>
+        <v>10000</v>
       </c>
       <c r="H28">
+        <v>100</v>
+      </c>
+      <c r="AF28">
         <v>10</v>
-      </c>
-      <c r="I28">
-        <v>10</v>
-      </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="O28">
-        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A29" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="C29">
-        <v>3000</v>
-      </c>
-      <c r="F29">
-        <v>850</v>
-      </c>
-      <c r="G29">
-        <v>1700</v>
-      </c>
-      <c r="AD29">
+        <v>10000</v>
+      </c>
+      <c r="I29">
         <v>100</v>
       </c>
-      <c r="BB29" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A30" t="s">
-        <v>183</v>
-      </c>
-      <c r="B30" t="s">
-        <v>145</v>
-      </c>
-      <c r="C30">
-        <v>5200</v>
-      </c>
-      <c r="F30">
-        <v>1500</v>
-      </c>
-      <c r="AG30">
-        <v>400</v>
-      </c>
-      <c r="AL30">
-        <v>25</v>
-      </c>
-      <c r="AZ30">
-        <v>100</v>
-      </c>
-      <c r="BA30" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A31" t="s">
-        <v>184</v>
-      </c>
-      <c r="B31" t="s">
-        <v>145</v>
-      </c>
-      <c r="C31">
-        <v>10000</v>
-      </c>
-      <c r="H31">
-        <v>100</v>
-      </c>
-      <c r="BB31" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A32" t="s">
-        <v>185</v>
-      </c>
-      <c r="B32" t="s">
-        <v>145</v>
-      </c>
-      <c r="C32">
-        <v>10000</v>
-      </c>
-      <c r="I32">
-        <v>100</v>
-      </c>
-      <c r="BA32" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="33" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A33" t="s">
-        <v>186</v>
-      </c>
-      <c r="B33" t="s">
-        <v>145</v>
-      </c>
-      <c r="C33">
-        <v>10000</v>
-      </c>
-      <c r="J33">
-        <v>100</v>
-      </c>
-      <c r="R33" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A34" t="s">
-        <v>187</v>
-      </c>
-      <c r="B34" t="s">
-        <v>144</v>
-      </c>
-      <c r="C34">
-        <v>10000</v>
-      </c>
-      <c r="N34">
-        <v>3</v>
-      </c>
-      <c r="BB34" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="35" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A35" t="s">
-        <v>188</v>
-      </c>
-      <c r="B35" t="s">
-        <v>145</v>
-      </c>
-      <c r="C35">
-        <v>10000</v>
-      </c>
-      <c r="F35">
-        <f>3000*2</f>
-        <v>6000</v>
-      </c>
-      <c r="S35">
-        <v>500</v>
-      </c>
-      <c r="T35">
-        <v>500</v>
-      </c>
-      <c r="AF35">
-        <v>10</v>
+      <c r="AZ29">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2992,65 +2839,65 @@
   <sheetData>
     <row r="1" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="BC1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="S2" t="s">
         <v>3</v>
       </c>
       <c r="U2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="AZ2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="K3" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="U3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="W3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="AB3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="AE3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="AG3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AI3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="AM3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.7">
@@ -3058,52 +2905,52 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O4" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q4" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" t="s">
-        <v>84</v>
-      </c>
-      <c r="L4" t="s">
-        <v>113</v>
-      </c>
-      <c r="M4" t="s">
-        <v>114</v>
-      </c>
-      <c r="N4" t="s">
-        <v>115</v>
-      </c>
-      <c r="O4" t="s">
-        <v>85</v>
-      </c>
-      <c r="P4" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>40</v>
       </c>
       <c r="R4" t="s">
         <v>2</v>
@@ -3112,120 +2959,120 @@
         <v>3</v>
       </c>
       <c r="T4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="U4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="V4" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="W4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="X4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="Z4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="AA4" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="AB4" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="AC4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AO4" t="s">
         <v>51</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AP4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR4" t="s">
         <v>50</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AS4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AU4" t="s">
         <v>57</v>
       </c>
-      <c r="AF4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI4" t="s">
+      <c r="AV4" t="s">
         <v>58</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AW4" t="s">
         <v>59</v>
       </c>
-      <c r="AK4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>71</v>
-      </c>
-      <c r="AT4" t="s">
+      <c r="AX4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>61</v>
+      </c>
+      <c r="AZ4" t="s">
         <v>72</v>
       </c>
-      <c r="AU4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>91</v>
-      </c>
       <c r="BA4" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="BB4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -3239,10 +3086,10 @@
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -3256,10 +3103,10 @@
     </row>
     <row r="7" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D7">
         <v>50</v>
@@ -3273,10 +3120,10 @@
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="E8">
         <v>50</v>
@@ -3287,10 +3134,10 @@
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E9">
         <v>50</v>
@@ -3307,10 +3154,10 @@
     </row>
     <row r="10" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -3321,10 +3168,10 @@
     </row>
     <row r="11" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E11">
         <v>200</v>
@@ -3335,10 +3182,10 @@
     </row>
     <row r="12" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D12">
         <v>150</v>
@@ -3355,10 +3202,10 @@
     </row>
     <row r="13" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D13">
         <v>400</v>
@@ -3369,10 +3216,10 @@
     </row>
     <row r="14" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E14">
         <v>1000</v>
@@ -3383,10 +3230,10 @@
     </row>
     <row r="15" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E15">
         <v>1000</v>
@@ -3397,10 +3244,10 @@
     </row>
     <row r="16" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E16">
         <v>1000</v>
@@ -3411,10 +3258,10 @@
     </row>
     <row r="17" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E17">
         <v>1000</v>
@@ -3425,10 +3272,10 @@
     </row>
     <row r="18" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E18">
         <v>1000</v>
@@ -3439,10 +3286,10 @@
     </row>
     <row r="19" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="D19">
         <v>1200</v>
@@ -3453,10 +3300,10 @@
     </row>
     <row r="20" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="D20">
         <v>1000</v>
@@ -3473,27 +3320,27 @@
     </row>
     <row r="21" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="D21">
         <v>1000</v>
       </c>
       <c r="R21" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="BA21" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A22" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="D22">
         <v>3000</v>
@@ -3504,128 +3351,128 @@
     </row>
     <row r="23" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A23" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="B23" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="BB23" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A24" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="E24">
         <v>300</v>
       </c>
       <c r="BB24" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A25" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="B25" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="D25">
         <v>200</v>
       </c>
       <c r="BB25" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A26" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="B26" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="D26">
         <v>300</v>
       </c>
       <c r="BB26" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A27" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B27" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="D27">
         <v>300</v>
       </c>
       <c r="BB27" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A28" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="D28">
         <v>300</v>
       </c>
       <c r="BB28" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A29" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="D29">
         <v>300</v>
       </c>
       <c r="BB29" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A30" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="D30">
         <v>300</v>
       </c>
       <c r="BB30" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A31" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="D31">
         <v>300</v>
       </c>
       <c r="BB31" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -3641,65 +3488,65 @@
   <sheetData>
     <row r="1" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="BC1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="S2" t="s">
         <v>3</v>
       </c>
       <c r="U2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="AZ2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="K3" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="U3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="W3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="AB3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="AE3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="AG3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AI3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="AM3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.7">
@@ -3707,52 +3554,52 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O4" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q4" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" t="s">
-        <v>84</v>
-      </c>
-      <c r="L4" t="s">
-        <v>113</v>
-      </c>
-      <c r="M4" t="s">
-        <v>114</v>
-      </c>
-      <c r="N4" t="s">
-        <v>115</v>
-      </c>
-      <c r="O4" t="s">
-        <v>85</v>
-      </c>
-      <c r="P4" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>40</v>
       </c>
       <c r="R4" t="s">
         <v>2</v>
@@ -3761,120 +3608,120 @@
         <v>3</v>
       </c>
       <c r="T4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="U4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="V4" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="W4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="X4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="Z4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="AA4" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="AB4" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="AC4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AO4" t="s">
         <v>51</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AP4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR4" t="s">
         <v>50</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AS4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AU4" t="s">
         <v>57</v>
       </c>
-      <c r="AF4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI4" t="s">
+      <c r="AV4" t="s">
         <v>58</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AW4" t="s">
         <v>59</v>
       </c>
-      <c r="AK4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>71</v>
-      </c>
-      <c r="AT4" t="s">
+      <c r="AX4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>61</v>
+      </c>
+      <c r="AZ4" t="s">
         <v>72</v>
       </c>
-      <c r="AU4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>91</v>
-      </c>
       <c r="BA4" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="BB4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>300</v>
@@ -3890,10 +3737,10 @@
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -3906,15 +3753,15 @@
         <v>2000</v>
       </c>
       <c r="BB6" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C7">
         <v>680</v>
@@ -3924,15 +3771,15 @@
         <v>4200</v>
       </c>
       <c r="BB7" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C8">
         <v>680</v>
@@ -3942,7 +3789,7 @@
         <v>1700</v>
       </c>
       <c r="BB8" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3958,65 +3805,65 @@
   <sheetData>
     <row r="1" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="BD1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:56" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="T2" t="s">
         <v>3</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="BA2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:56" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="L3" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="V3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="X3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="AC3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="AH3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="AN3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:56" x14ac:dyDescent="0.7">
@@ -4024,55 +3871,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" t="s">
+        <v>93</v>
+      </c>
+      <c r="N4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O4" t="s">
+        <v>95</v>
+      </c>
+      <c r="P4" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>96</v>
+      </c>
+      <c r="R4" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s">
-        <v>84</v>
-      </c>
-      <c r="M4" t="s">
-        <v>113</v>
-      </c>
-      <c r="N4" t="s">
-        <v>114</v>
-      </c>
-      <c r="O4" t="s">
-        <v>115</v>
-      </c>
-      <c r="P4" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>116</v>
-      </c>
-      <c r="R4" t="s">
-        <v>40</v>
       </c>
       <c r="S4" t="s">
         <v>2</v>
@@ -4081,120 +3928,120 @@
         <v>3</v>
       </c>
       <c r="U4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="V4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="W4" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="X4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="AA4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="AB4" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="AC4" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="AD4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP4" t="s">
         <v>51</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AQ4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS4" t="s">
         <v>50</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AT4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV4" t="s">
         <v>57</v>
       </c>
-      <c r="AG4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AJ4" t="s">
+      <c r="AW4" t="s">
         <v>58</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AX4" t="s">
         <v>59</v>
       </c>
-      <c r="AL4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>71</v>
-      </c>
-      <c r="AU4" t="s">
+      <c r="AY4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>61</v>
+      </c>
+      <c r="BA4" t="s">
         <v>72</v>
       </c>
-      <c r="AV4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>77</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>91</v>
-      </c>
       <c r="BB4" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="BC4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C5">
         <v>160</v>
@@ -4205,10 +4052,10 @@
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C6">
         <v>680</v>
@@ -4219,10 +4066,10 @@
     </row>
     <row r="7" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C7">
         <v>1600</v>
@@ -4233,10 +4080,10 @@
     </row>
     <row r="8" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C8">
         <v>3000</v>
@@ -4247,10 +4094,10 @@
     </row>
     <row r="9" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C9">
         <v>4500</v>
@@ -4261,10 +4108,10 @@
     </row>
     <row r="10" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C10">
         <v>7500</v>
@@ -4275,10 +4122,10 @@
     </row>
     <row r="11" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C11">
         <v>12800</v>
@@ -4300,65 +4147,65 @@
   <sheetData>
     <row r="1" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="BD1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:56" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="T2" t="s">
         <v>3</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="BA2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:56" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="L3" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="V3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="X3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="AC3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="AH3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="AN3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:56" x14ac:dyDescent="0.7">
@@ -4366,55 +4213,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" t="s">
+        <v>93</v>
+      </c>
+      <c r="N4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O4" t="s">
+        <v>95</v>
+      </c>
+      <c r="P4" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>96</v>
+      </c>
+      <c r="R4" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s">
-        <v>84</v>
-      </c>
-      <c r="M4" t="s">
-        <v>113</v>
-      </c>
-      <c r="N4" t="s">
-        <v>114</v>
-      </c>
-      <c r="O4" t="s">
-        <v>115</v>
-      </c>
-      <c r="P4" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>116</v>
-      </c>
-      <c r="R4" t="s">
-        <v>40</v>
       </c>
       <c r="S4" t="s">
         <v>2</v>
@@ -4423,120 +4270,120 @@
         <v>3</v>
       </c>
       <c r="U4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="V4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="W4" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="X4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="AA4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="AB4" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="AC4" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="AD4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP4" t="s">
         <v>51</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AQ4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS4" t="s">
         <v>50</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AT4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV4" t="s">
         <v>57</v>
       </c>
-      <c r="AG4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AJ4" t="s">
+      <c r="AW4" t="s">
         <v>58</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AX4" t="s">
         <v>59</v>
       </c>
-      <c r="AL4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>71</v>
-      </c>
-      <c r="AU4" t="s">
+      <c r="AY4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>61</v>
+      </c>
+      <c r="BA4" t="s">
         <v>72</v>
       </c>
-      <c r="AV4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>77</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>91</v>
-      </c>
       <c r="BB4" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="BC4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -4550,10 +4397,10 @@
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="C6">
         <v>160</v>
@@ -4570,10 +4417,10 @@
     </row>
     <row r="7" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C7">
         <v>300</v>
@@ -4596,10 +4443,10 @@
     </row>
     <row r="8" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C8">
         <v>680</v>
@@ -4619,10 +4466,10 @@
     </row>
     <row r="9" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C9">
         <v>1000</v>
@@ -4642,10 +4489,10 @@
     </row>
     <row r="10" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="B10" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C10">
         <v>2400</v>
@@ -4659,10 +4506,10 @@
     </row>
     <row r="11" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C11">
         <v>2400</v>
@@ -4679,10 +4526,10 @@
     </row>
     <row r="12" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C12">
         <v>5200</v>
@@ -4707,65 +4554,65 @@
   <sheetData>
     <row r="1" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="BD1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:56" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="T2" t="s">
         <v>3</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="BA2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:56" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="L3" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="V3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="X3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="AC3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="AH3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="AN3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:56" x14ac:dyDescent="0.7">
@@ -4773,55 +4620,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" t="s">
+        <v>93</v>
+      </c>
+      <c r="N4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O4" t="s">
+        <v>95</v>
+      </c>
+      <c r="P4" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>96</v>
+      </c>
+      <c r="R4" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s">
-        <v>84</v>
-      </c>
-      <c r="M4" t="s">
-        <v>113</v>
-      </c>
-      <c r="N4" t="s">
-        <v>114</v>
-      </c>
-      <c r="O4" t="s">
-        <v>115</v>
-      </c>
-      <c r="P4" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>116</v>
-      </c>
-      <c r="R4" t="s">
-        <v>40</v>
       </c>
       <c r="S4" t="s">
         <v>2</v>
@@ -4830,120 +4677,120 @@
         <v>3</v>
       </c>
       <c r="U4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="V4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="W4" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="X4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="AA4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="AB4" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="AC4" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="AD4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP4" t="s">
         <v>51</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AQ4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS4" t="s">
         <v>50</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AT4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV4" t="s">
         <v>57</v>
       </c>
-      <c r="AG4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AJ4" t="s">
+      <c r="AW4" t="s">
         <v>58</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AX4" t="s">
         <v>59</v>
       </c>
-      <c r="AL4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>71</v>
-      </c>
-      <c r="AU4" t="s">
+      <c r="AY4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>61</v>
+      </c>
+      <c r="BA4" t="s">
         <v>72</v>
       </c>
-      <c r="AV4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>77</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>91</v>
-      </c>
       <c r="BB4" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="BC4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -4952,15 +4799,15 @@
         <v>100</v>
       </c>
       <c r="BB5" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>300</v>
@@ -4983,10 +4830,10 @@
     </row>
     <row r="7" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>300</v>
@@ -5009,10 +4856,10 @@
     </row>
     <row r="8" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C8">
         <v>1000</v>
@@ -5032,10 +4879,10 @@
     </row>
     <row r="9" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C9">
         <v>2400</v>
@@ -5044,21 +4891,21 @@
         <v>600</v>
       </c>
       <c r="X9" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="Y9">
         <v>1500</v>
       </c>
       <c r="BB9" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C10">
         <v>1000</v>
@@ -5067,7 +4914,7 @@
         <v>300</v>
       </c>
       <c r="X10" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="AB10">
         <v>20</v>
@@ -5075,10 +4922,10 @@
     </row>
     <row r="11" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="B11" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C11">
         <v>3000</v>
@@ -5092,10 +4939,10 @@
     </row>
     <row r="12" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A12" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="B12" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C12">
         <v>5200</v>
@@ -5109,10 +4956,10 @@
     </row>
     <row r="13" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A13" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="B13" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C13">
         <v>10000</v>
@@ -5129,10 +4976,10 @@
     </row>
     <row r="14" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="B14" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C14">
         <v>10000</v>
@@ -5141,7 +4988,7 @@
         <v>100</v>
       </c>
       <c r="BC14" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -5157,65 +5004,65 @@
   <sheetData>
     <row r="1" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="BD1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:56" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="T2" t="s">
         <v>3</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="BA2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:56" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="L3" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="V3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="X3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="AC3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="AH3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="AN3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:56" x14ac:dyDescent="0.7">
@@ -5223,55 +5070,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" t="s">
+        <v>93</v>
+      </c>
+      <c r="N4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O4" t="s">
+        <v>95</v>
+      </c>
+      <c r="P4" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>96</v>
+      </c>
+      <c r="R4" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s">
-        <v>84</v>
-      </c>
-      <c r="M4" t="s">
-        <v>113</v>
-      </c>
-      <c r="N4" t="s">
-        <v>114</v>
-      </c>
-      <c r="O4" t="s">
-        <v>115</v>
-      </c>
-      <c r="P4" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>116</v>
-      </c>
-      <c r="R4" t="s">
-        <v>40</v>
       </c>
       <c r="S4" t="s">
         <v>2</v>
@@ -5280,120 +5127,120 @@
         <v>3</v>
       </c>
       <c r="U4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="V4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="W4" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="X4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="AA4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="AB4" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="AC4" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="AD4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP4" t="s">
         <v>51</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AQ4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS4" t="s">
         <v>50</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AT4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV4" t="s">
         <v>57</v>
       </c>
-      <c r="AG4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AJ4" t="s">
+      <c r="AW4" t="s">
         <v>58</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AX4" t="s">
         <v>59</v>
       </c>
-      <c r="AL4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>71</v>
-      </c>
-      <c r="AU4" t="s">
+      <c r="AY4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>61</v>
+      </c>
+      <c r="BA4" t="s">
         <v>72</v>
       </c>
-      <c r="AV4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>77</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>91</v>
-      </c>
       <c r="BB4" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="BC4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C5">
         <v>3000</v>
@@ -5418,15 +5265,15 @@
         <v>8</v>
       </c>
       <c r="BC5" t="s">
-        <v>208</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>209</v>
+        <v>161</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C6">
         <v>3000</v>
@@ -5438,15 +5285,15 @@
         <v>40</v>
       </c>
       <c r="BC6" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>211</v>
+        <v>162</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C7">
         <v>1600</v>
@@ -5461,7 +5308,7 @@
         <v>8</v>
       </c>
       <c r="S7" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="T7">
         <v>450</v>
@@ -5500,10 +5347,10 @@
         <v>1</v>
       </c>
       <c r="BB7" t="s">
-        <v>212</v>
+        <v>163</v>
       </c>
       <c r="BC7" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kinop\Documents\Billing-Planning-for-Trickcal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEB7F55-DDE3-4C59-9A11-582EABD06086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC13571-8154-4DF6-89D4-4595B49A4306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{0E240044-467D-4804-AB3F-8E98DCC96A0D}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="184">
   <si>
     <t>商品名</t>
     <rPh sb="0" eb="3">
@@ -121,10 +121,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>たっぷり私服コーデ箱</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>無料エリーフ</t>
     <rPh sb="0" eb="2">
       <t>ムリョウ</t>
@@ -222,20 +218,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>※1000</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1000エリーフは構成品の中から選ぶことで獲得可能</t>
-    <rPh sb="9" eb="11">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ヒン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>エルダイン使徒合成カード</t>
     <rPh sb="5" eb="7">
       <t>シト</t>
@@ -1203,10 +1185,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>たっぷり私服コーデ箱*1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>週間無料パック</t>
     <rPh sb="0" eb="2">
       <t>シュウカン</t>
@@ -1258,10 +1236,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>7000K</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ジョアン：私服パス</t>
     <rPh sb="5" eb="7">
       <t>シフク</t>
@@ -1358,133 +1332,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>一緒にずっとロビーパック</t>
-    <rPh sb="0" eb="2">
-      <t>イッショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ウサギトークン*3,ロビー背景 一緒にずっと(昼)*1</t>
-    <rPh sb="13" eb="15">
-      <t>ハイケイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>イッショ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ヒル</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>１周年キャンディパック</t>
-    <rPh sb="1" eb="3">
-      <t>シュウネン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1周年たっぷりパック</t>
-    <rPh sb="1" eb="3">
-      <t>シュウネン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ウサギトークン*2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘイリーの挨拶パック</t>
-    <rPh sb="5" eb="7">
-      <t>アイサツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘイリーの交渉パック</t>
-    <rPh sb="5" eb="7">
-      <t>コウショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘイリーの満足パック</t>
-    <rPh sb="5" eb="7">
-      <t>マンゾク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘイリーの進級パック</t>
-    <rPh sb="5" eb="7">
-      <t>シンキュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘイリーの装備パック</t>
-    <rPh sb="5" eb="7">
-      <t>ソウビ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>星に願い事ヨミパック</t>
-    <rPh sb="0" eb="1">
-      <t>ホシ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ネガ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ゴト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘイリーの指揮パック</t>
-    <rPh sb="5" eb="7">
-      <t>シキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘイリーのイキりパック</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヘイリーの意思パック</t>
-    <rPh sb="5" eb="7">
-      <t>イシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>★3所持一般使徒選択チケット</t>
-    <rPh sb="2" eb="4">
-      <t>ショジ</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>イッパンシト</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヨミの使徒証*20</t>
-    <rPh sb="3" eb="5">
-      <t>シト</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>魔法!疑いの眼差し</t>
     <rPh sb="0" eb="2">
       <t>マホウ</t>
@@ -1605,71 +1452,84 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>コミーの秘密パック</t>
-    <rPh sb="4" eb="6">
-      <t>ヒミツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コミーの休息パック</t>
-    <rPh sb="4" eb="6">
-      <t>キュウソク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コミーの足跡パック</t>
-    <rPh sb="4" eb="6">
-      <t>アシアト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コミーの計画パック</t>
-    <rPh sb="4" eb="6">
-      <t>ケイカク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コミーの水遊びパック</t>
-    <rPh sb="4" eb="6">
-      <t>ミズアソ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コミーの目標パック</t>
-    <rPh sb="4" eb="6">
-      <t>モクヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コミーの満足パック</t>
-    <rPh sb="4" eb="6">
-      <t>マンゾク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コミーのスカウトパック</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コミーの回想パック</t>
-    <rPh sb="4" eb="6">
-      <t>カイソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1500K</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ウサギトークン*5</t>
+    <t>グヴィンのときめきパック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グヴィンの好奇心パック</t>
+    <rPh sb="5" eb="8">
+      <t>コウキシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グヴィンの征服パック</t>
+    <rPh sb="5" eb="7">
+      <t>セイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グヴィンの悲しさパック</t>
+    <rPh sb="5" eb="6">
+      <t>カナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グヴィンの疑問パック</t>
+    <rPh sb="5" eb="7">
+      <t>ギモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グヴィンの助言パック</t>
+    <rPh sb="5" eb="7">
+      <t>ジョゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グヴィンの装備パック</t>
+    <rPh sb="5" eb="7">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グヴィンの夢パック</t>
+    <rPh sb="5" eb="6">
+      <t>ユメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グヴィンの足取りパック</t>
+    <rPh sb="5" eb="7">
+      <t>アシド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>伝説カードガチャ*2</t>
+    <rPh sb="0" eb="2">
+      <t>デンセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">希少、伝説カードガチャチケット </t>
+    <rPh sb="0" eb="2">
+      <t>キショウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>デンセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スパビタF</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2054,70 +1914,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E721CC5-3751-4AD8-8501-A75691DE05E7}">
-  <dimension ref="A1:BC29"/>
+  <dimension ref="A1:BC16"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <sheetData>
     <row r="1" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="BC1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="S2" t="s">
         <v>3</v>
       </c>
       <c r="U2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AZ2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="U3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="W3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AB3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM3" t="s">
         <v>46</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.7">
@@ -2125,52 +1985,52 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>15</v>
       </c>
-      <c r="J4" t="s">
-        <v>16</v>
-      </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L4" t="s">
+        <v>90</v>
+      </c>
+      <c r="M4" t="s">
+        <v>91</v>
+      </c>
+      <c r="N4" t="s">
+        <v>92</v>
+      </c>
+      <c r="O4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" t="s">
         <v>93</v>
       </c>
-      <c r="M4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N4" t="s">
-        <v>95</v>
-      </c>
-      <c r="O4" t="s">
-        <v>68</v>
-      </c>
-      <c r="P4" t="s">
-        <v>96</v>
-      </c>
       <c r="Q4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R4" t="s">
         <v>2</v>
@@ -2179,112 +2039,112 @@
         <v>3</v>
       </c>
       <c r="T4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U4" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" t="s">
+        <v>29</v>
+      </c>
+      <c r="X4" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB4" t="s">
         <v>30</v>
       </c>
-      <c r="V4" t="s">
+      <c r="AC4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD4" t="s">
         <v>31</v>
       </c>
-      <c r="W4" t="s">
-        <v>32</v>
-      </c>
-      <c r="X4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC4" t="s">
+      <c r="AE4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG4" t="s">
         <v>35</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AH4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>183</v>
+      </c>
+      <c r="AL4" t="s">
         <v>34</v>
       </c>
-      <c r="AE4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>37</v>
-      </c>
       <c r="AM4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AN4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AU4" t="s">
         <v>54</v>
       </c>
-      <c r="AO4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AS4" t="s">
+      <c r="AV4" t="s">
         <v>55</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AW4" t="s">
         <v>56</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AX4" t="s">
         <v>57</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AY4" t="s">
         <v>58</v>
       </c>
-      <c r="AW4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AX4" t="s">
+      <c r="AZ4" t="s">
+        <v>69</v>
+      </c>
+      <c r="BA4" t="s">
         <v>60</v>
       </c>
-      <c r="AY4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>63</v>
-      </c>
       <c r="BB4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.7">
@@ -2292,16 +2152,16 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C5">
         <v>160</v>
       </c>
       <c r="R5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.7">
@@ -2309,7 +2169,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C6">
         <v>680</v>
@@ -2326,7 +2186,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C7">
         <v>1600</v>
@@ -2338,7 +2198,7 @@
         <v>10</v>
       </c>
       <c r="R7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>300</v>
@@ -2347,7 +2207,7 @@
         <v>300</v>
       </c>
       <c r="W7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="X7">
         <v>1500</v>
@@ -2355,47 +2215,62 @@
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>172</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C8">
-        <v>680</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
-      </c>
-      <c r="BB8" t="s">
-        <v>151</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>23</v>
+        <v>300</v>
+      </c>
+      <c r="F8">
+        <v>80</v>
+      </c>
+      <c r="G8">
+        <v>80</v>
+      </c>
+      <c r="S8">
+        <v>200</v>
+      </c>
+      <c r="X8">
+        <v>500</v>
+      </c>
+      <c r="AK8">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C9">
-        <v>160</v>
-      </c>
-      <c r="R9" t="s">
-        <v>11</v>
-      </c>
-      <c r="S9">
-        <v>1111</v>
+        <v>300</v>
+      </c>
+      <c r="F9">
+        <v>80</v>
+      </c>
+      <c r="G9">
+        <v>80</v>
+      </c>
+      <c r="T9">
+        <v>100</v>
+      </c>
+      <c r="AA9">
+        <v>3</v>
+      </c>
+      <c r="AK9">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C10">
         <v>1000</v>
@@ -2403,427 +2278,122 @@
       <c r="F10">
         <v>300</v>
       </c>
-      <c r="G10">
-        <v>300</v>
-      </c>
-      <c r="S10">
-        <v>300</v>
-      </c>
-      <c r="T10">
-        <v>300</v>
+      <c r="H10">
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>2000</v>
-      </c>
-      <c r="AF10">
-        <v>2</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>169</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C11">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F11">
-        <v>850</v>
-      </c>
-      <c r="H11">
+        <v>300</v>
+      </c>
+      <c r="J11">
         <v>10</v>
       </c>
-      <c r="I11">
-        <v>10</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>166</v>
+      <c r="R11" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C12">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F12">
-        <v>300</v>
+        <v>850</v>
       </c>
       <c r="G12">
-        <v>300</v>
-      </c>
-      <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="BB12" t="s">
-        <v>150</v>
+        <v>850</v>
       </c>
     </row>
     <row r="13" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A13" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C13">
-        <v>1000</v>
+        <v>5200</v>
       </c>
       <c r="F13">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="G13">
-        <v>300</v>
-      </c>
-      <c r="I13">
-        <v>10</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>150</v>
+        <v>1500</v>
+      </c>
+      <c r="AG13">
+        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A14" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C14">
-        <v>1000</v>
+        <v>5200</v>
       </c>
       <c r="F14">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="G14">
-        <v>300</v>
-      </c>
-      <c r="J14">
-        <v>10</v>
-      </c>
-      <c r="BB14" t="s">
-        <v>150</v>
+        <v>1500</v>
+      </c>
+      <c r="W14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A15" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15">
-        <v>3000</v>
-      </c>
-      <c r="F15">
-        <v>850</v>
-      </c>
-      <c r="AE15">
-        <v>10</v>
-      </c>
-      <c r="AF15">
-        <v>4</v>
+        <v>10000</v>
+      </c>
+      <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="L15">
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A16" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C16">
-        <v>5200</v>
-      </c>
-      <c r="F16">
-        <v>1500</v>
-      </c>
-      <c r="G16">
-        <v>1500</v>
-      </c>
-      <c r="W16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A17" t="s">
-        <v>175</v>
-      </c>
-      <c r="B17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17">
         <v>10000</v>
       </c>
-      <c r="BA17" t="s">
-        <v>158</v>
-      </c>
-      <c r="BB17" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A18" t="s">
-        <v>176</v>
-      </c>
-      <c r="B18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18">
-        <v>12800</v>
-      </c>
-      <c r="H18">
-        <v>150</v>
-      </c>
-      <c r="R18" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A19" t="s">
-        <v>177</v>
-      </c>
-      <c r="B19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19">
-        <v>12800</v>
-      </c>
-      <c r="I19">
-        <v>150</v>
-      </c>
-      <c r="K19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A20" t="s">
-        <v>178</v>
-      </c>
-      <c r="B20" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20">
-        <v>12800</v>
-      </c>
-      <c r="J20">
-        <v>150</v>
-      </c>
-      <c r="R20" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A21" t="s">
-        <v>193</v>
-      </c>
-      <c r="B21" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21">
-        <v>300</v>
-      </c>
-      <c r="F21">
-        <v>80</v>
-      </c>
-      <c r="S21">
+      <c r="J16">
         <v>100</v>
       </c>
-      <c r="T21">
-        <v>100</v>
-      </c>
-      <c r="AI21">
-        <v>10</v>
-      </c>
-      <c r="AZ21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A22" t="s">
-        <v>194</v>
-      </c>
-      <c r="B22" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22">
-        <v>1000</v>
-      </c>
-      <c r="F22">
-        <v>300</v>
-      </c>
-      <c r="AQ22">
-        <v>90</v>
-      </c>
-      <c r="AT22">
-        <v>30</v>
-      </c>
-      <c r="AV22">
-        <v>150</v>
-      </c>
-      <c r="AX22">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A23" t="s">
-        <v>195</v>
-      </c>
-      <c r="B23" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23">
-        <v>1000</v>
-      </c>
-      <c r="F23">
-        <v>300</v>
-      </c>
-      <c r="G23">
-        <v>300</v>
-      </c>
-      <c r="AF23">
-        <v>1</v>
-      </c>
-      <c r="BB23" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A24" t="s">
-        <v>196</v>
-      </c>
-      <c r="B24" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24">
-        <v>2400</v>
-      </c>
-      <c r="F24">
-        <v>600</v>
-      </c>
-      <c r="H24">
-        <v>10</v>
-      </c>
-      <c r="I24">
-        <v>10</v>
-      </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-      <c r="BA24" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A25" t="s">
-        <v>197</v>
-      </c>
-      <c r="B25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25">
-        <v>2400</v>
-      </c>
-      <c r="F25">
-        <v>600</v>
-      </c>
-      <c r="S25">
-        <v>600</v>
-      </c>
-      <c r="T25">
-        <v>600</v>
-      </c>
-      <c r="AZ25">
-        <v>40</v>
-      </c>
-      <c r="BB25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A26" t="s">
-        <v>198</v>
-      </c>
-      <c r="B26" t="s">
-        <v>126</v>
-      </c>
-      <c r="C26">
-        <v>5200</v>
-      </c>
-      <c r="F26">
-        <v>1500</v>
-      </c>
-      <c r="S26">
-        <v>500</v>
-      </c>
-      <c r="T26">
-        <v>500</v>
-      </c>
-      <c r="AG26">
-        <v>400</v>
-      </c>
-      <c r="BB26" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="27" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A27" t="s">
-        <v>199</v>
-      </c>
-      <c r="B27" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27">
-        <v>10000</v>
-      </c>
-      <c r="G27">
-        <v>100</v>
-      </c>
-      <c r="L27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A28" t="s">
-        <v>200</v>
-      </c>
-      <c r="B28" t="s">
-        <v>125</v>
-      </c>
-      <c r="C28">
-        <v>10000</v>
-      </c>
-      <c r="H28">
-        <v>100</v>
-      </c>
-      <c r="AF28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A29" t="s">
-        <v>201</v>
-      </c>
-      <c r="B29" t="s">
-        <v>125</v>
-      </c>
-      <c r="C29">
-        <v>10000</v>
-      </c>
-      <c r="I29">
-        <v>100</v>
-      </c>
-      <c r="AZ29">
-        <v>200</v>
+      <c r="R16" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2839,65 +2409,65 @@
   <sheetData>
     <row r="1" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="BC1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="S2" t="s">
         <v>3</v>
       </c>
       <c r="U2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AZ2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="U3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="W3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AB3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM3" t="s">
         <v>46</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.7">
@@ -2905,52 +2475,52 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>15</v>
       </c>
-      <c r="J4" t="s">
-        <v>16</v>
-      </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L4" t="s">
+        <v>90</v>
+      </c>
+      <c r="M4" t="s">
+        <v>91</v>
+      </c>
+      <c r="N4" t="s">
+        <v>92</v>
+      </c>
+      <c r="O4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" t="s">
         <v>93</v>
       </c>
-      <c r="M4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N4" t="s">
-        <v>95</v>
-      </c>
-      <c r="O4" t="s">
-        <v>68</v>
-      </c>
-      <c r="P4" t="s">
-        <v>96</v>
-      </c>
       <c r="Q4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R4" t="s">
         <v>2</v>
@@ -2959,120 +2529,120 @@
         <v>3</v>
       </c>
       <c r="T4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U4" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" t="s">
+        <v>29</v>
+      </c>
+      <c r="X4" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB4" t="s">
         <v>30</v>
       </c>
-      <c r="V4" t="s">
+      <c r="AC4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD4" t="s">
         <v>31</v>
       </c>
-      <c r="W4" t="s">
-        <v>32</v>
-      </c>
-      <c r="X4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC4" t="s">
+      <c r="AE4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG4" t="s">
         <v>35</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AH4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL4" t="s">
         <v>34</v>
       </c>
-      <c r="AE4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>37</v>
-      </c>
       <c r="AM4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AN4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AU4" t="s">
         <v>54</v>
       </c>
-      <c r="AO4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AS4" t="s">
+      <c r="AV4" t="s">
         <v>55</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AW4" t="s">
         <v>56</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AX4" t="s">
         <v>57</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AY4" t="s">
         <v>58</v>
       </c>
-      <c r="AW4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AX4" t="s">
+      <c r="AZ4" t="s">
+        <v>69</v>
+      </c>
+      <c r="BA4" t="s">
         <v>60</v>
       </c>
-      <c r="AY4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>63</v>
-      </c>
       <c r="BB4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -3086,10 +2656,10 @@
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -3103,10 +2673,10 @@
     </row>
     <row r="7" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D7">
         <v>50</v>
@@ -3120,10 +2690,10 @@
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E8">
         <v>50</v>
@@ -3134,10 +2704,10 @@
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E9">
         <v>50</v>
@@ -3154,10 +2724,10 @@
     </row>
     <row r="10" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -3168,10 +2738,10 @@
     </row>
     <row r="11" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E11">
         <v>200</v>
@@ -3182,10 +2752,10 @@
     </row>
     <row r="12" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D12">
         <v>150</v>
@@ -3202,10 +2772,10 @@
     </row>
     <row r="13" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D13">
         <v>400</v>
@@ -3216,10 +2786,10 @@
     </row>
     <row r="14" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E14">
         <v>1000</v>
@@ -3230,10 +2800,10 @@
     </row>
     <row r="15" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E15">
         <v>1000</v>
@@ -3244,10 +2814,10 @@
     </row>
     <row r="16" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E16">
         <v>1000</v>
@@ -3258,10 +2828,10 @@
     </row>
     <row r="17" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E17">
         <v>1000</v>
@@ -3272,10 +2842,10 @@
     </row>
     <row r="18" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E18">
         <v>1000</v>
@@ -3286,10 +2856,10 @@
     </row>
     <row r="19" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D19">
         <v>1200</v>
@@ -3300,10 +2870,10 @@
     </row>
     <row r="20" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D20">
         <v>1000</v>
@@ -3320,27 +2890,27 @@
     </row>
     <row r="21" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" t="s">
         <v>89</v>
-      </c>
-      <c r="B21" t="s">
-        <v>92</v>
       </c>
       <c r="D21">
         <v>1000</v>
       </c>
       <c r="R21" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="BA21" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D22">
         <v>3000</v>
@@ -3351,128 +2921,128 @@
     </row>
     <row r="23" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A23" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="BB23" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A24" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E24">
         <v>300</v>
       </c>
       <c r="BB24" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A25" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B25" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D25">
         <v>200</v>
       </c>
       <c r="BB25" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A26" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D26">
         <v>300</v>
       </c>
       <c r="BB26" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A27" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D27">
         <v>300</v>
       </c>
       <c r="BB27" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A28" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D28">
         <v>300</v>
       </c>
       <c r="BB28" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A29" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D29">
         <v>300</v>
       </c>
       <c r="BB29" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D30">
         <v>300</v>
       </c>
       <c r="BB30" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.7">
       <c r="A31" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D31">
         <v>300</v>
       </c>
       <c r="BB31" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -3488,65 +3058,65 @@
   <sheetData>
     <row r="1" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="BC1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="S2" t="s">
         <v>3</v>
       </c>
       <c r="U2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AZ2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="U3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="W3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AB3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM3" t="s">
         <v>46</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.7">
@@ -3554,52 +3124,52 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>15</v>
       </c>
-      <c r="J4" t="s">
-        <v>16</v>
-      </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L4" t="s">
+        <v>90</v>
+      </c>
+      <c r="M4" t="s">
+        <v>91</v>
+      </c>
+      <c r="N4" t="s">
+        <v>92</v>
+      </c>
+      <c r="O4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" t="s">
         <v>93</v>
       </c>
-      <c r="M4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N4" t="s">
-        <v>95</v>
-      </c>
-      <c r="O4" t="s">
-        <v>68</v>
-      </c>
-      <c r="P4" t="s">
-        <v>96</v>
-      </c>
       <c r="Q4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R4" t="s">
         <v>2</v>
@@ -3608,120 +3178,120 @@
         <v>3</v>
       </c>
       <c r="T4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U4" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" t="s">
+        <v>29</v>
+      </c>
+      <c r="X4" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB4" t="s">
         <v>30</v>
       </c>
-      <c r="V4" t="s">
+      <c r="AC4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD4" t="s">
         <v>31</v>
       </c>
-      <c r="W4" t="s">
-        <v>32</v>
-      </c>
-      <c r="X4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC4" t="s">
+      <c r="AE4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG4" t="s">
         <v>35</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AH4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL4" t="s">
         <v>34</v>
       </c>
-      <c r="AE4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>37</v>
-      </c>
       <c r="AM4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AN4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AU4" t="s">
         <v>54</v>
       </c>
-      <c r="AO4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AS4" t="s">
+      <c r="AV4" t="s">
         <v>55</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AW4" t="s">
         <v>56</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AX4" t="s">
         <v>57</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AY4" t="s">
         <v>58</v>
       </c>
-      <c r="AW4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AX4" t="s">
+      <c r="AZ4" t="s">
+        <v>69</v>
+      </c>
+      <c r="BA4" t="s">
         <v>60</v>
       </c>
-      <c r="AY4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>72</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>63</v>
-      </c>
       <c r="BB4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C5">
         <v>300</v>
@@ -3737,10 +3307,10 @@
     </row>
     <row r="6" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -3753,15 +3323,15 @@
         <v>2000</v>
       </c>
       <c r="BB6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C7">
         <v>680</v>
@@ -3771,15 +3341,15 @@
         <v>4200</v>
       </c>
       <c r="BB7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C8">
         <v>680</v>
@@ -3789,7 +3359,7 @@
         <v>1700</v>
       </c>
       <c r="BB8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -3805,65 +3375,65 @@
   <sheetData>
     <row r="1" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="BD1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:56" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="T2" t="s">
         <v>3</v>
       </c>
       <c r="V2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AJ2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="BA2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:56" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="V3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="X3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AC3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN3" t="s">
         <v>46</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:56" x14ac:dyDescent="0.7">
@@ -3871,55 +3441,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
         <v>14</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>15</v>
       </c>
-      <c r="K4" t="s">
-        <v>16</v>
-      </c>
       <c r="L4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M4" t="s">
+        <v>90</v>
+      </c>
+      <c r="N4" t="s">
+        <v>91</v>
+      </c>
+      <c r="O4" t="s">
+        <v>92</v>
+      </c>
+      <c r="P4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" t="s">
         <v>93</v>
       </c>
-      <c r="N4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O4" t="s">
-        <v>95</v>
-      </c>
-      <c r="P4" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>96</v>
-      </c>
       <c r="R4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S4" t="s">
         <v>2</v>
@@ -3928,120 +3498,120 @@
         <v>3</v>
       </c>
       <c r="U4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V4" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC4" t="s">
         <v>30</v>
       </c>
-      <c r="W4" t="s">
+      <c r="AD4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE4" t="s">
         <v>31</v>
       </c>
-      <c r="X4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>142</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD4" t="s">
+      <c r="AF4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH4" t="s">
         <v>35</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AI4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AM4" t="s">
         <v>34</v>
       </c>
-      <c r="AF4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>37</v>
-      </c>
       <c r="AN4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AO4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AV4" t="s">
         <v>54</v>
       </c>
-      <c r="AP4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AT4" t="s">
+      <c r="AW4" t="s">
         <v>55</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AX4" t="s">
         <v>56</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AY4" t="s">
         <v>57</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AZ4" t="s">
         <v>58</v>
       </c>
-      <c r="AX4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AY4" t="s">
+      <c r="BA4" t="s">
+        <v>69</v>
+      </c>
+      <c r="BB4" t="s">
         <v>60</v>
       </c>
-      <c r="AZ4" t="s">
-        <v>61</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>72</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>63</v>
-      </c>
       <c r="BC4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C5">
         <v>160</v>
@@ -4052,10 +3622,10 @@
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C6">
         <v>680</v>
@@ -4066,10 +3636,10 @@
     </row>
     <row r="7" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C7">
         <v>1600</v>
@@ -4080,10 +3650,10 @@
     </row>
     <row r="8" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C8">
         <v>3000</v>
@@ -4094,10 +3664,10 @@
     </row>
     <row r="9" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C9">
         <v>4500</v>
@@ -4108,10 +3678,10 @@
     </row>
     <row r="10" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C10">
         <v>7500</v>
@@ -4122,10 +3692,10 @@
     </row>
     <row r="11" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C11">
         <v>12800</v>
@@ -4147,65 +3717,65 @@
   <sheetData>
     <row r="1" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="BD1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:56" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="T2" t="s">
         <v>3</v>
       </c>
       <c r="V2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AJ2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="BA2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:56" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="V3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="X3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AC3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN3" t="s">
         <v>46</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:56" x14ac:dyDescent="0.7">
@@ -4213,55 +3783,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
         <v>14</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>15</v>
       </c>
-      <c r="K4" t="s">
-        <v>16</v>
-      </c>
       <c r="L4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M4" t="s">
+        <v>90</v>
+      </c>
+      <c r="N4" t="s">
+        <v>91</v>
+      </c>
+      <c r="O4" t="s">
+        <v>92</v>
+      </c>
+      <c r="P4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" t="s">
         <v>93</v>
       </c>
-      <c r="N4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O4" t="s">
-        <v>95</v>
-      </c>
-      <c r="P4" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>96</v>
-      </c>
       <c r="R4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S4" t="s">
         <v>2</v>
@@ -4270,120 +3840,120 @@
         <v>3</v>
       </c>
       <c r="U4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V4" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC4" t="s">
         <v>30</v>
       </c>
-      <c r="W4" t="s">
+      <c r="AD4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE4" t="s">
         <v>31</v>
       </c>
-      <c r="X4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>142</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD4" t="s">
+      <c r="AF4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH4" t="s">
         <v>35</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AI4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AM4" t="s">
         <v>34</v>
       </c>
-      <c r="AF4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>37</v>
-      </c>
       <c r="AN4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AO4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AV4" t="s">
         <v>54</v>
       </c>
-      <c r="AP4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AT4" t="s">
+      <c r="AW4" t="s">
         <v>55</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AX4" t="s">
         <v>56</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AY4" t="s">
         <v>57</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AZ4" t="s">
         <v>58</v>
       </c>
-      <c r="AX4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AY4" t="s">
+      <c r="BA4" t="s">
+        <v>69</v>
+      </c>
+      <c r="BB4" t="s">
         <v>60</v>
       </c>
-      <c r="AZ4" t="s">
-        <v>61</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>72</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>63</v>
-      </c>
       <c r="BC4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -4397,10 +3967,10 @@
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C6">
         <v>160</v>
@@ -4417,10 +3987,10 @@
     </row>
     <row r="7" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C7">
         <v>300</v>
@@ -4443,10 +4013,10 @@
     </row>
     <row r="8" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C8">
         <v>680</v>
@@ -4466,10 +4036,10 @@
     </row>
     <row r="9" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C9">
         <v>1000</v>
@@ -4489,10 +4059,10 @@
     </row>
     <row r="10" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" t="s">
         <v>119</v>
-      </c>
-      <c r="B10" t="s">
-        <v>122</v>
       </c>
       <c r="C10">
         <v>2400</v>
@@ -4506,10 +4076,10 @@
     </row>
     <row r="11" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C11">
         <v>2400</v>
@@ -4526,10 +4096,10 @@
     </row>
     <row r="12" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A12" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C12">
         <v>5200</v>
@@ -4554,65 +4124,65 @@
   <sheetData>
     <row r="1" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="BD1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:56" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="T2" t="s">
         <v>3</v>
       </c>
       <c r="V2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AJ2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="BA2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:56" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="V3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="X3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AC3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN3" t="s">
         <v>46</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:56" x14ac:dyDescent="0.7">
@@ -4620,55 +4190,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
         <v>14</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>15</v>
       </c>
-      <c r="K4" t="s">
-        <v>16</v>
-      </c>
       <c r="L4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M4" t="s">
+        <v>90</v>
+      </c>
+      <c r="N4" t="s">
+        <v>91</v>
+      </c>
+      <c r="O4" t="s">
+        <v>92</v>
+      </c>
+      <c r="P4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" t="s">
         <v>93</v>
       </c>
-      <c r="N4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O4" t="s">
-        <v>95</v>
-      </c>
-      <c r="P4" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>96</v>
-      </c>
       <c r="R4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S4" t="s">
         <v>2</v>
@@ -4677,120 +4247,120 @@
         <v>3</v>
       </c>
       <c r="U4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V4" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC4" t="s">
         <v>30</v>
       </c>
-      <c r="W4" t="s">
+      <c r="AD4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE4" t="s">
         <v>31</v>
       </c>
-      <c r="X4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>142</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD4" t="s">
+      <c r="AF4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH4" t="s">
         <v>35</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AI4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AM4" t="s">
         <v>34</v>
       </c>
-      <c r="AF4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>37</v>
-      </c>
       <c r="AN4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AO4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AV4" t="s">
         <v>54</v>
       </c>
-      <c r="AP4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AT4" t="s">
+      <c r="AW4" t="s">
         <v>55</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AX4" t="s">
         <v>56</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AY4" t="s">
         <v>57</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AZ4" t="s">
         <v>58</v>
       </c>
-      <c r="AX4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AY4" t="s">
+      <c r="BA4" t="s">
+        <v>69</v>
+      </c>
+      <c r="BB4" t="s">
         <v>60</v>
       </c>
-      <c r="AZ4" t="s">
-        <v>61</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>72</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>63</v>
-      </c>
       <c r="BC4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -4799,15 +4369,15 @@
         <v>100</v>
       </c>
       <c r="BB5" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C6">
         <v>300</v>
@@ -4830,10 +4400,10 @@
     </row>
     <row r="7" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C7">
         <v>300</v>
@@ -4856,10 +4426,10 @@
     </row>
     <row r="8" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C8">
         <v>1000</v>
@@ -4879,10 +4449,10 @@
     </row>
     <row r="9" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C9">
         <v>2400</v>
@@ -4891,21 +4461,21 @@
         <v>600</v>
       </c>
       <c r="X9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="Y9">
         <v>1500</v>
       </c>
       <c r="BB9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C10">
         <v>1000</v>
@@ -4914,7 +4484,7 @@
         <v>300</v>
       </c>
       <c r="X10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AB10">
         <v>20</v>
@@ -4922,10 +4492,10 @@
     </row>
     <row r="11" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C11">
         <v>3000</v>
@@ -4939,10 +4509,10 @@
     </row>
     <row r="12" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" t="s">
         <v>134</v>
-      </c>
-      <c r="B12" t="s">
-        <v>137</v>
       </c>
       <c r="C12">
         <v>5200</v>
@@ -4956,10 +4526,10 @@
     </row>
     <row r="13" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C13">
         <v>10000</v>
@@ -4976,10 +4546,10 @@
     </row>
     <row r="14" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C14">
         <v>10000</v>
@@ -4988,7 +4558,7 @@
         <v>100</v>
       </c>
       <c r="BC14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -5004,65 +4574,65 @@
   <sheetData>
     <row r="1" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="BD1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:56" x14ac:dyDescent="0.7">
       <c r="C2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="T2" t="s">
         <v>3</v>
       </c>
       <c r="V2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AJ2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="BA2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:56" x14ac:dyDescent="0.7">
       <c r="D3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="V3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="X3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AC3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN3" t="s">
         <v>46</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:56" x14ac:dyDescent="0.7">
@@ -5070,55 +4640,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
         <v>14</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>15</v>
       </c>
-      <c r="K4" t="s">
-        <v>16</v>
-      </c>
       <c r="L4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M4" t="s">
+        <v>90</v>
+      </c>
+      <c r="N4" t="s">
+        <v>91</v>
+      </c>
+      <c r="O4" t="s">
+        <v>92</v>
+      </c>
+      <c r="P4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" t="s">
         <v>93</v>
       </c>
-      <c r="N4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O4" t="s">
-        <v>95</v>
-      </c>
-      <c r="P4" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>96</v>
-      </c>
       <c r="R4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S4" t="s">
         <v>2</v>
@@ -5127,120 +4697,120 @@
         <v>3</v>
       </c>
       <c r="U4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V4" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" t="s">
+        <v>28</v>
+      </c>
+      <c r="X4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC4" t="s">
         <v>30</v>
       </c>
-      <c r="W4" t="s">
+      <c r="AD4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE4" t="s">
         <v>31</v>
       </c>
-      <c r="X4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>142</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD4" t="s">
+      <c r="AF4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH4" t="s">
         <v>35</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AI4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AM4" t="s">
         <v>34</v>
       </c>
-      <c r="AF4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>37</v>
-      </c>
       <c r="AN4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AO4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AV4" t="s">
         <v>54</v>
       </c>
-      <c r="AP4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AT4" t="s">
+      <c r="AW4" t="s">
         <v>55</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AX4" t="s">
         <v>56</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AY4" t="s">
         <v>57</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AZ4" t="s">
         <v>58</v>
       </c>
-      <c r="AX4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AY4" t="s">
+      <c r="BA4" t="s">
+        <v>69</v>
+      </c>
+      <c r="BB4" t="s">
         <v>60</v>
       </c>
-      <c r="AZ4" t="s">
-        <v>61</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>72</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>63</v>
-      </c>
       <c r="BC4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C5">
         <v>3000</v>
@@ -5265,15 +4835,15 @@
         <v>8</v>
       </c>
       <c r="BC5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C6">
         <v>3000</v>
@@ -5285,15 +4855,15 @@
         <v>40</v>
       </c>
       <c r="BC6" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C7">
         <v>1600</v>
@@ -5308,7 +4878,7 @@
         <v>8</v>
       </c>
       <c r="S7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T7">
         <v>450</v>
@@ -5347,10 +4917,10 @@
         <v>1</v>
       </c>
       <c r="BB7" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="BC7" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kinop\Documents\Billing-Planning-for-Trickcal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC13571-8154-4DF6-89D4-4595B49A4306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CCD2D7-B863-4C1B-BA38-2A20FDC90329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{0E240044-467D-4804-AB3F-8E98DCC96A0D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{0E240044-467D-4804-AB3F-8E98DCC96A0D}"/>
   </bookViews>
   <sheets>
     <sheet name="特別構成商品" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="169">
   <si>
     <t>商品名</t>
     <rPh sb="0" eb="3">
@@ -1157,34 +1157,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>イベント・日/1回</t>
-    <rPh sb="5" eb="6">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>カイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ウサギトークン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>イベント・日/5回</t>
-    <rPh sb="5" eb="6">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>カイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ウサギトークン*1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>週間無料パック</t>
     <rPh sb="0" eb="2">
       <t>シュウカン</t>
@@ -1328,107 +1300,6 @@
     </rPh>
     <rPh sb="59" eb="62">
       <t>ザイリョウバコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魔法!疑いの眼差し</t>
-    <rPh sb="0" eb="2">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ウタガ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>マナザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>月光変身!ヨミポスター</t>
-    <rPh sb="0" eb="4">
-      <t>ゲッコウヘンシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魔法少女と戦うヴィヴィフィギュア</t>
-    <rPh sb="0" eb="4">
-      <t>マホウショウジョ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>タタカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魔法少女と戦うヨミフィギュア</t>
-    <rPh sb="0" eb="4">
-      <t>マホウショウジョ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>タタカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>月にかかった魔法少女</t>
-    <rPh sb="0" eb="1">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="6" eb="10">
-      <t>マホウショウジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魔法少女ヨミフレーム</t>
-    <rPh sb="0" eb="4">
-      <t>マホウショウジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ポスター:魔法!疑いの眼差し</t>
-    <rPh sb="5" eb="7">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ウタガ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>マナザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ポスター月光変身!ヨミポスター</t>
-    <rPh sb="4" eb="8">
-      <t>ゲッコウヘンシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フィギュア:魔法少女と戦うヴィヴィのフィギュア</t>
-    <rPh sb="6" eb="10">
-      <t>マホウショウジョ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>タタカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フィギュア:魔法少女と戦うヨミのフィギュア</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>キーホルダー:月にかかった魔法少女</t>
-    <rPh sb="7" eb="8">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>マホウショウジョ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1991,10 +1862,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -2090,7 +1961,7 @@
         <v>40</v>
       </c>
       <c r="AK4" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="AL4" t="s">
         <v>34</v>
@@ -2152,7 +2023,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C5">
         <v>160</v>
@@ -2169,7 +2040,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C6">
         <v>680</v>
@@ -2186,7 +2057,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C7">
         <v>1600</v>
@@ -2215,7 +2086,7 @@
     </row>
     <row r="8" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="B8" t="s">
         <v>122</v>
@@ -2241,7 +2112,7 @@
     </row>
     <row r="9" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="B9" t="s">
         <v>122</v>
@@ -2267,7 +2138,7 @@
     </row>
     <row r="10" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
         <v>122</v>
@@ -2287,7 +2158,7 @@
     </row>
     <row r="11" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="B11" t="s">
         <v>122</v>
@@ -2302,12 +2173,12 @@
         <v>10</v>
       </c>
       <c r="R11" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s">
         <v>122</v>
@@ -2324,7 +2195,7 @@
     </row>
     <row r="13" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A13" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s">
         <v>123</v>
@@ -2344,7 +2215,7 @@
     </row>
     <row r="14" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s">
         <v>121</v>
@@ -2364,7 +2235,7 @@
     </row>
     <row r="15" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A15" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s">
         <v>122</v>
@@ -2381,7 +2252,7 @@
     </row>
     <row r="16" spans="1:55" x14ac:dyDescent="0.7">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s">
         <v>122</v>
@@ -2393,7 +2264,7 @@
         <v>100</v>
       </c>
       <c r="R16" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2404,7 +2275,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B812215E-6864-47F5-89FE-632A3D1823AF}">
-  <dimension ref="A1:BC31"/>
+  <dimension ref="A1:BC22"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <sheetData>
     <row r="1" spans="1:55" x14ac:dyDescent="0.7">
@@ -2481,10 +2352,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -2826,7 +2697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.7">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.7">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -2840,7 +2711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.7">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.7">
       <c r="A18" t="s">
         <v>83</v>
       </c>
@@ -2854,7 +2725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.7">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.7">
       <c r="A19" t="s">
         <v>84</v>
       </c>
@@ -2868,7 +2739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.7">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.7">
       <c r="A20" t="s">
         <v>85</v>
       </c>
@@ -2888,7 +2759,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.7">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.7">
       <c r="A21" t="s">
         <v>86</v>
       </c>
@@ -2905,7 +2776,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.7">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.7">
       <c r="A22" t="s">
         <v>87</v>
       </c>
@@ -2917,132 +2788,6 @@
       </c>
       <c r="Q22">
         <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A23" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" t="s">
-        <v>144</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A24" t="s">
-        <v>145</v>
-      </c>
-      <c r="B24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E24">
-        <v>300</v>
-      </c>
-      <c r="BB24" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A25" t="s">
-        <v>145</v>
-      </c>
-      <c r="B25" t="s">
-        <v>146</v>
-      </c>
-      <c r="D25">
-        <v>200</v>
-      </c>
-      <c r="BB25" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A26" t="s">
-        <v>160</v>
-      </c>
-      <c r="B26" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26">
-        <v>300</v>
-      </c>
-      <c r="BB26" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="27" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A27" t="s">
-        <v>161</v>
-      </c>
-      <c r="B27" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27">
-        <v>300</v>
-      </c>
-      <c r="BB27" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="28" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A28" t="s">
-        <v>162</v>
-      </c>
-      <c r="B28" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28">
-        <v>300</v>
-      </c>
-      <c r="BB28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A29" t="s">
-        <v>163</v>
-      </c>
-      <c r="B29" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29">
-        <v>300</v>
-      </c>
-      <c r="BB29" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A30" t="s">
-        <v>164</v>
-      </c>
-      <c r="B30" t="s">
-        <v>121</v>
-      </c>
-      <c r="D30">
-        <v>300</v>
-      </c>
-      <c r="BB30" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.7">
-      <c r="A31" t="s">
-        <v>165</v>
-      </c>
-      <c r="B31" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31">
-        <v>300</v>
-      </c>
-      <c r="BB31" t="s">
-        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -3130,10 +2875,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -3447,10 +3192,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -3789,10 +3534,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -3950,7 +3695,7 @@
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s">
         <v>88</v>
@@ -4196,10 +3941,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -4357,7 +4102,7 @@
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
         <v>89</v>
@@ -4369,7 +4114,7 @@
         <v>100</v>
       </c>
       <c r="BB5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.7">
@@ -4646,10 +4391,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -4807,7 +4552,7 @@
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B5" t="s">
         <v>121</v>
@@ -4835,12 +4580,12 @@
         <v>8</v>
       </c>
       <c r="BC5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
         <v>121</v>
@@ -4855,12 +4600,12 @@
         <v>40</v>
       </c>
       <c r="BC6" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:56" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B7" t="s">
         <v>121</v>
@@ -4917,10 +4662,10 @@
         <v>1</v>
       </c>
       <c r="BB7" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="BC7" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
